--- a/processed_ruby_restored_xlsx/sc032a_３日目：ノノ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032a_３日目：ノノ.ss.xlsx
@@ -515,8 +515,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>I'm sure she still has it herself, but if she's not in
-her room, then where on earth did she go？</t>
+          <t>I'm sure she still has it herself, but if she's not
+in her room, then where on earth did she go？</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -547,8 +547,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>It can't possibly be in Miru-chan and Rin-chan's room,
-right...?</t>
+          <t>It can't possibly be in Miru-chan and Rin-chan's
+room, right...?</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,8 +563,9 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>If they're all gathered again continuing their reading
-club, it'd be really awkward to ask for it back.</t>
+          <t>If they're all gathered again continuing their
+reading club, it'd be really awkward to ask for it
+back.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -857,8 +858,8 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>While I was heading to the toilet and stepped into the
-washroom, I heard the sound of a shower.</t>
+          <t>While I was heading to the toilet and stepped into
+the washroom, I heard the sound of a shower.</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -888,8 +889,8 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>The laundry basket had today's clothes for everyone in
-it, so I couldn't tell who was in there.</t>
+          <t>The laundry basket had today's clothes for everyone
+in it, so I couldn't tell who was in there.</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1317,7 +1318,8 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>This time she muttered to herself with a puzzled face.</t>
+          <t>This time she muttered to herself with a puzzled
+face.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1502,7 +1504,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Because what she's doing is undeniably masturbation...</t>
+          <t>Because what she's doing is undeniably
+masturbation...</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1580,8 +1583,8 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Hearing Nono-chan mutter that, I felt like I knew what
-she was thinking.</t>
+          <t>Hearing Nono-chan mutter that, I felt like I knew
+what she was thinking.</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1597,8 +1600,8 @@
       <c r="B74" s="1" t="inlineStr">
         <is>
           <t>I tried using erotic books as a manual, but the real
-feeling has to be totally different from what's in the
-book...</t>
+feeling has to be totally different from what's in
+the book...</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1643,8 +1646,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>「Uh, hmm… what was that girl in that book doing again…
-hmm, uhh—！」</t>
+          <t>「Uh, hmm… what was that girl in that book doing
+again… hmm, uhh—！」</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1859,7 +1862,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan said that as she turned the shower on there.</t>
+          <t>Nono-chan said that as she turned the shower on
+there.</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1996,8 +2000,8 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Ah… I see. Running the shower over herself is to cover
-up her embarrassment.</t>
+          <t>Ah… I see. Running the shower over herself is to
+cover up her embarrassment.</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2012,8 +2016,8 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>The sound of water splashing distracts you, and if the
-worst happens you can always say you were just
+          <t>The sound of water splashing distracts you, and if
+the worst happens you can always say you were just
 washing.</t>
         </is>
       </c>
@@ -2059,8 +2063,8 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>...As expected, Nono-chan becomes more absorbed in the
-act.</t>
+          <t>...As expected, Nono-chan becomes more absorbed in
+the act.</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2106,8 +2110,8 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>「I-It's... like this, right...? I-If it's like this, I
-might be convinced...！」</t>
+          <t>「I-It's... like this, right...? I-If it's like this,
+I might be convinced...！」</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2737,8 +2741,8 @@
       <c r="B148" s="1" t="inlineStr">
         <is>
           <t>She'd probably been starting to understand things
-vaguely, but she still hadn't clearly realized that it
-felt good….</t>
+vaguely, but she still hadn't clearly realized that
+it felt good….</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2874,8 +2878,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Then she made a sour face and started rinsing her body
-under the shower.</t>
+          <t>Then she made a sour face and started rinsing her
+body under the shower.</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2890,8 +2894,8 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>It seemed like she was trying to wash away feelings of
-embarrassment, regret, and the like.</t>
+          <t>It seemed like she was trying to wash away feelings
+of embarrassment, regret, and the like.</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3046,9 +3050,9 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Because her sexual interest and intellectual curiosity
-were mixed together, she had been seriously applying
-herself to sex.</t>
+          <t>Because her sexual interest and intellectual
+curiosity were mixed together, she had been seriously
+applying herself to sex.</t>
         </is>
       </c>
       <c r="C168" t="n">

--- a/processed_ruby_restored_xlsx/sc032a_３日目：ノノ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032a_３日目：ノノ.ss.xlsx
@@ -499,8 +499,8 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Since I took it from her, I can't imagine she'd hand
-something I confiscated to another girl.</t>
+          <t>Since I took it from Nono-chan, I can't imagine she'd
+pass the confiscated item on to another girl.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Not here, then...</t>
+          <t>Isn't it here...?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -733,8 +733,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Watching quietly, Rurichiyo-chan went into her room
-without noticing me.</t>
+          <t>I watched quietly as Rurichiyo-chan went into her
+room without noticing me.</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -764,8 +764,8 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Then I guess the possibility of it being a reading
-group disappears.</t>
+          <t>That would rule out the idea that they're all
+gathered for a reading club, I guess.</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -780,8 +780,8 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>It's possible they were having a book club and only
-Rurichiyo-chan came out, but I'll leave that for
+          <t>It's possible they were having a reading club and
+only Rurichiyo-chan came out, but I'll leave that for
 later.</t>
         </is>
       </c>
@@ -813,7 +813,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>So, where else could they be…?</t>
+          <t>So, where else could she be...?</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -858,8 +858,8 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>While I was heading to the toilet and stepped into
-the washroom, I heard the sound of a shower.</t>
+          <t>When I went into the washroom on my way to the
+toilet, I heard someone taking a shower.</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>「Muuu~~... Uuuuuu...！」</t>
+          <t>"Mmm... Uuuu...!"</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>I heard Nono-chan's low, whining voice from inside.</t>
+          <t>From inside, I heard Nono-chan moaning.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan must have been in the bath...。</t>
+          <t>So Nono-chan was in the bath...</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -996,8 +996,8 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Just as I thought that and was about to go back to my
-room.</t>
+          <t>Just as I was thinking that and about to head back to
+my room.</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>「Nn... kyafun！」</t>
+          <t>"Mmm... kyah!"</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's popping voice made my body go rigid.</t>
+          <t>I froze at Nono-chan's bursting cry.</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Wh... that voice just now...？</t>
+          <t>W-what was that voice just now...?</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1102,8 +1102,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>I felt pulled toward the bathroom, opened the door
-quietly...</t>
+          <t>I was drawn to the bathroom and quietly opened the
+door...</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, uuu~~~...」</t>
+          <t>「Mmm... uuu~~~...」</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1178,8 +1178,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Peeking through the gap in the door, I was hit with a
-huge shock.</t>
+          <t>Peeking through the crack in the door, I was stunned.</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1210,9 +1209,8 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>And she held the shower head in her right hand, while
-her left hand was... unbelievably, reaching between
-her legs.</t>
+          <t>Nono-chan held the shower head in her right hand,
+while her left hand was... reaching between her legs.</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1242,7 +1240,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, hiyuu... muu, uuu...」</t>
+          <t>「Ugh... hii... mmm... uuu~~~...」</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1272,8 +1270,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>What she was doing was obvious at a glance, but her
-action and expression didn't quite match.</t>
+          <t>What Nono-chan was doing was obvious at a glance, but
+her actions and expression didn't quite match.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1318,8 +1316,8 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>This time she muttered to herself with a puzzled
-face.</t>
+          <t>This time Nono-chan was muttering to herself with a
+troubled expression.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1334,8 +1332,8 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Can't be satisfied — with the thing she's doing right
-now... right？</t>
+          <t>When she says she 'can't be satisfied,' she means the
+act she's doing right now... right?</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1365,7 +1363,8 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>「I-If I do it like this... th-this... uuu...！」</t>
+          <t>「I-If I'm not mistaken, if I do it here like this...
+ooo...!」</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1380,7 +1379,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan slid her finger toward her slit...</t>
+          <t>Nono-chan inserted her finger into Wareme-san...</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1395,8 +1394,8 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Or so I thought, but she only inserted it up to the
-first knuckle, twisted her face, and pulled her hand
+          <t>But just when I thought that, she only inserted it up
+to the first knuckle, grimaced, and pulled her hand
 back.</t>
         </is>
       </c>
@@ -1427,8 +1426,8 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, uuu...！ N-no, maybe it's still wrong... muu,
-uuu...！」</t>
+          <t>Mmm... uuu...! Y-yeah, as I thought, maybe
+something's still off... muu, uuu...!</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1473,7 +1472,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>What's going on... she's getting mad at herself.</t>
+          <t>What's this... she's getting angry all by herself.</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1504,8 +1503,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Because what she's doing is undeniably
-masturbation...</t>
+          <t>After all, what she's doing is undeniably
+masturbating...</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1535,9 +1534,9 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>She's such an inquisitive kid that maybe she saw a
-dirty book and wanted to see if it was really like
-that...？</t>
+          <t>Nono-chan is such an intellectually curious girl that
+maybe she saw an erotic book and wanted to see if it
+was really like that...?</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1567,8 +1566,8 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>「Mmm… it just feels all sharp and tingly… W-will this
-really make me feel good…？」</t>
+          <t>"Mmm… it just feels sharp and tingly… W-will this
+really make me feel good…?"</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1599,9 +1598,9 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>I tried using erotic books as a manual, but the real
-feeling has to be totally different from what's in
-the book...</t>
+          <t>I tried using an erotic book as a manual, but the
+real sensation is probably a lot different from
+what's in it...</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1616,7 +1615,8 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Well, sticking a finger in right away... yeah？</t>
+          <t>Well, you can't just stick a finger in right away...
+can you?</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1646,8 +1646,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>「Uh, hmm… what was that girl in that book doing
-again… hmm, uhh—！」</t>
+          <t>「U-um... how did the girl in that book do it again...
+hmm, uuu—!」</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>…Hmm, I want to tell you.</t>
+          <t>…Hmm... I want to tell her.</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>I really want to teach you, step by step！</t>
+          <t>I want to teach you step by step!</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1724,8 +1724,8 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>If she realized I was here, her embarrassment would
-explode and she'd probably lose it.</t>
+          <t>If she realized I was here, I'd be so embarrassed I'd
+probably freak out.</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>For now, I can only watch over you...</t>
+          <t>For now, I'll just watch...</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1770,8 +1770,8 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>「…Right, I see — you can't just do it all of a
-sudden…！」</t>
+          <t>"…Oh — that's right, you can't just do it right
+away…!"</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>「Uu... i-it's ticklish...」</t>
+          <t>「Uu... I-it's ticklish...」</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan said that as she turned the shower on
+          <t>While saying that, Nono-chan aimed the shower down
 there.</t>
         </is>
       </c>
@@ -1878,8 +1878,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>What is she thinking？ It's not like she's trying to
-wash away her juices with the hot water...</t>
+          <t>What is she up to? It's not like she's trying to wash
+away her love juices with hot water...</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>「Fuu... nnng... nng, nn...」</t>
+          <t>「Huu... nnng... nng, nng...」</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1924,8 +1924,8 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan is rubbing around her slit while aiming the
-shower at it.</t>
+          <t>Nono-chan is rubbing the area around the slit between
+her legs while directing the shower at it.</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「Nn, fuu… nn… fuu, fuu… ah, nn…」</t>
+          <t>「Nn... Huu... nn... Huu, Huu... nn...」</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2000,8 +2000,8 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Ah… I see. Running the shower over herself is to
-cover up her embarrassment.</t>
+          <t>Ah... I see. She's aiming the shower down there to
+hide her embarrassment.</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2016,9 +2016,9 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>The sound of water splashing distracts you, and if
-the worst happens you can always say you were just
-washing.</t>
+          <t>The sound of the splashing water helps cover it up,
+and if anything happens she can always say she was
+just washing.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>「…huh, fuu…n, nnn…！ n！」</t>
+          <t>「…Huu... nn... nnn...! Nn!」</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2079,8 +2079,9 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>I knead the soft area around the slit with my finger,
-continuing to give gentle stimulation.</t>
+          <t>Nono-chan kneads the soft area around the slit
+between her legs with her finger, continuing to give
+it gentle stimulation.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2110,8 +2111,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>「I-It's... like this, right...? I-If it's like this,
-I might be convinced...！」</t>
+          <t>"I-It's... like this, right...? This might do it...!"</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2126,9 +2126,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>Y-Yes, as expected of Nono-chan... she's putting into
-practice what she learned from those naughty books
-really well！</t>
+          <t>As expected of Nono-chan... she's really putting into
+practice what she picked up from those naughty books!</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2143,8 +2142,8 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Besides, from where I stand, having the shower on her
-is a major plus.</t>
+          <t>Besides, from where I’m standing, the fact that she’s
+directing the shower down there is a big plus.</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2190,7 +2189,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>「...hh... fuu...！ Yeah... uff, fuu...！」</t>
+          <t>「…Huu…! Nn… uff, Huu…!」</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,7 +2219,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Has she realized this feels good？</t>
+          <t>Is she starting to realize this feels good?</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2265,7 +2264,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>「Huu... nn, nnh... huu, huu... faa, ah... ah, aaah！？」</t>
+          <t>「Huu... n! nngh... huu, huu... fah, ah... ah, aaah!?」</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2280,8 +2279,8 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan let out a big breath, then her body gave a
-sudden shudder and froze.</t>
+          <t>Nono-chan exhaled deeply; her body gave a sudden
+shudder and she stopped moving.</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2296,7 +2295,8 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>She stayed like that, cheeks flushed.</t>
+          <t>Nono-chan remained in that position, her cheeks
+flushed.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan said softly, looking down.</t>
+          <t>Nono-chan softly lowers her eyes and says.</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2356,8 +2356,8 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>No matter how much she tried to fool herself, she
-still thought what she was doing was embarrassing….</t>
+          <t>No matter how much she tries to fool herself, she
+still thinks she's doing something embarrassing…</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>「Ah… uu, uuu…！」</t>
+          <t>「…uh… uuu…！」</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan let out a breath like a groan.</t>
+          <t>Nono-chan exhaled with a groan.</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ku, uuu… fu, fuu… n, nn…」</t>
+          <t>「…kuh… uuh… fuh, fuu… nn, nnh…」</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2463,8 +2463,8 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>She began rubbing between her legs again, letting out
-hesitant breaths.</t>
+          <t>Nono-chan began rubbing between her legs again,
+letting out a hesitant breath.</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>「Nn… y-yeah… I forgot about this….」</t>
+          <t>「Nn… y-yes… I forgot about this…」</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2509,8 +2509,8 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>That line sparked a small idea in me, and I strained
-my eyes.</t>
+          <t>At those words, a faint idea occurred to me, and I
+peered closer.</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2541,7 +2541,8 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>And then she discovered something buried inside—.</t>
+          <t>And then I discovered something that had been buried
+inside—</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2571,7 +2572,7 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>「Nfuuhhh！？」</t>
+          <t>「Nnfuuh！？」</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2602,8 +2603,8 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>She'd just touched the girl's most sensitive
-O-mame-san….</t>
+          <t>I'd just touched the girl's most sensitive
+O-mame-san...</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2633,7 +2634,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>「W-what, wha…！ What was that just now…！?」</t>
+          <t>"W-what...!? What was that just now...?!"</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2695,7 +2696,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>「…Uu… n, nnh~…」</t>
+          <t>「…uuh… nn, nnh~…」</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2710,7 +2711,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's eyes took on a light like regret.</t>
+          <t>Nono-chan's eyes took on a look of regret.</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2740,9 +2741,9 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>She'd probably been starting to understand things
-vaguely, but she still hadn't clearly realized that
-it felt good….</t>
+          <t>Nono-chan had probably started to get a vague sense
+of it, but she still hadn't clearly realized that it
+felt good….</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2757,7 +2758,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Still, Nono-chan had done her best.</t>
+          <t>Still, Nono-chan did her best in her own way.</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2772,8 +2773,8 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>She'd thought things through herself, tried them out,
-and this was the result, so it couldn't be helped.</t>
+          <t>I think she thought things through and tried various
+things herself, so it couldn't be helped.</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2788,7 +2789,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>I wish I could really teach her properly….</t>
+          <t>I wish I could teach her properly...</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2818,7 +2819,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>「Fwaa… let's stop already….」</t>
+          <t>"Sigh... Let's stop now..."</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2863,7 +2864,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>「U... muu...」</t>
+          <t>"U... mmm..."</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2878,8 +2879,8 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Then she made a sour face and started rinsing her
-body under the shower.</t>
+          <t>Then, grimacing, she began to rinse herself off in
+the shower.</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2910,8 +2911,8 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Maybe because of those feelings, Nono-chan held the
-shower directly over her between (her) legs.</t>
+          <t>Perhaps because of those feelings, Nono-chan aimed
+the shower directly between her legs.</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2941,7 +2942,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>「Hya！？　Hiu...！！？」</t>
+          <t>Eek!? Uuh...!?</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2956,9 +2957,9 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan received the shower's fierce droplets
-directly on her between (her) legs, froze with a
-shocked expression...</t>
+          <t>Nono-chan felt the shower's strong spray hit her
+directly between her legs and froze with a shocked
+expression...</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3034,8 +3035,8 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>...No, still, even after she masturbated, she's still
-Nono-chan, isn't she...</t>
+          <t>…But even so, even though Nono-chan masturbated,
+she's still Nono-chan, isn't she...</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3050,9 +3051,8 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Because her sexual interest and intellectual
-curiosity were mixed together, she had been seriously
-applying herself to sex.</t>
+          <t>Because my sexual interest and intellectual curiosity
+were intertwined, I had been earnestly exploring sex.</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3067,8 +3067,9 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>But her sexual knowledge is shallow for all that, so
-she ends up doing kind of clueless things...</t>
+          <t>But despite that, Nono-chan's sexual knowledge is
+shallow, so she ends up doing sort of clueless/naive
+things...</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3098,7 +3099,8 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>I want to teach her by hand, by foot, by hip！</t>
+          <t>I want to teach her thoroughly—with my hands, my
+feet, and my hips!</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3143,8 +3145,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>...I stood up, holding down the penis that had gotten
-hard.</t>
+          <t>I stood up, pressing down on my now-hard penis.</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3159,7 +3160,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>A-anyway, let's get back to the room.</t>
+          <t>A-anyway, let's go back to the room.</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3174,8 +3175,8 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Comic RO doesn't have the vibe today where I can say,
-'give it back.'</t>
+          <t>As for Comic RO, today isn't the kind of day when I
+can ask for it back.</t>
         </is>
       </c>
       <c r="C176" t="n">
